--- a/data/reference/zhugeshenshuan_jq.xlsx
+++ b/data/reference/zhugeshenshuan_jq.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K384"/>
+  <dimension ref="A1:K385"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24834,6 +24834,33 @@
         </is>
       </c>
     </row>
+    <row r="385">
+      <c r="A385" t="n">
+        <v>384</v>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>中上签</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>兑宫 小过变恒（小过六二）</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>人非孔颜，鲜能无过，过而能改，仍复无过，开花不足凭，结果方为准，放开怀抱意欣欣。</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr"/>
+      <c r="F385" t="inlineStr"/>
+      <c r="G385" t="inlineStr"/>
+      <c r="H385" t="inlineStr"/>
+      <c r="I385" t="inlineStr"/>
+      <c r="J385" t="inlineStr"/>
+      <c r="K385" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/reference/zhugeshenshuan_jq.xlsx
+++ b/data/reference/zhugeshenshuan_jq.xlsx
@@ -690,7 +690,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>春花娇媚，不禁雨打风飘，秋菊幽芳，反耐霜凌雪傲。</t>
+          <t>春花娇媚，不禁雨打风飘；秋菊幽芳，反耐霜凌雪傲。</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>鼎沸起风波，孤舟要渡河，巧中却藏拙，人事转蹉跎。</t>
+          <t>鼎沸起风波，孤舟要渡河，巧中藏却拙，人事转蹉跎。</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>见不见，也防人背面，遇不遇，到底无凭据。</t>
+          <t>见不见，也防人背面；遇不遇，到底无凭据。</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>一番桃李一番春，谁识当初气象新，林下水边寻活计，见山了了称心意。</t>
+          <t>一番桃李一番春，谁识当初气象新。林下水边寻活计，见山了了称心意。</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>倾一杯，展??愁眉，天地合，好思为。</t>
+          <t>倾一杯，展愁眉，天地合，好思为。</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>可以寄百里之命，可以托六尺之孤，钟期既遇毋迟误。笑呼呼，乡聚首，各自乐康和。</t>
+          <t>可以寄百里之命，可以托六尺之孤，钟期既遇毋迟误。笑呼呼，他乡聚首，各自乐康。</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -8245,7 +8245,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>宝镜新，照两人，心中结，合同心。</t>
+          <t>宝镜亲照两人，心中结，合同心。</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -9398,7 +9398,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>利在中邦出战时，一番获馈在王庭，凤衔丹诏归阳畔，得享佳名四海荣。</t>
+          <t>利在中邦出战征，一番获丑在王庭，凤衔丹诏归阳畔，得享佳名四海荣。</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -9529,7 +9529,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>一重山一重水，风波道坦然，壸中有别天。</t>
+          <t>一重水一重山，风波道坦然，壶中别有天。</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -9653,7 +9653,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>船棹中流急，花开春又离，事宁心不静，惹起许多疑。</t>
+          <t>船棹中流急，花开春又逢，事宁心不静，惹起许多疑。</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -10979,7 +10979,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>大事可成功，有益还无咎，云中执鞭人，报在三秋后）。</t>
+          <t>大事可成功，有益还无咎，云中执鞭人，报在三秋后。</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -12558,7 +12558,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>事苦羁留，人不出头，往来闭塞，要见无有。</t>
+          <t>事若羁留，人不出头，往来闭塞，要见无有。</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -13839,7 +13839,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>望去几重山，高深渐可攀，举头天上看，明月在人间。</t>
+          <t>望去几重山，高深渐可攀，举头天上看，明月出人间。</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -13901,7 +13901,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>用之则行，舍之则藏，一骑出重关，佳音咫尺间。</t>
+          <t>用之则行，舍之则藏，一骑出重门，佳音咫尺间。</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -14089,7 +14089,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>门内起干戈，亲仇两不和，朱衣??临日月，始觉笑呵呵。</t>
+          <t>门内起干戈，亲仇两不和，朱衣临日月，始觉笑呵呵。</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -14727,7 +14727,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>佳信至，开笑颜，飞腾一去，拨云上天。</t>
+          <t>佳信至，开笑颜，飞腾一去，披云上天。</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -15303,7 +15303,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>道路狂招呼，风波一点无，时乖心绪乱，全仗贵人扶。</t>
+          <t>道路在招呼，风波一点无，时乖心绪乱，全仗贵人扶。</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -16663,7 +16663,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>东南北将来成故墟，燕蓟地苍生无存济，若要大奋雄心，水源不知何处？</t>
+          <t>东南地将来成故墟，燕蓟地苍生无存济，若要大奋雄心，水源不知何处？</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -17114,7 +17114,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>数尾金鱼吞饵，丝竿钓了回头，家食翻嫌太贵，五湖四海遨游。</t>
+          <t>数尾金鱼吞饵，丝竿钓了回头，家食翻嫌太费，五湖四海遨游。</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -17940,7 +17940,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>来去原无定处，时来时去安身，跋涉无虑，荣辱不计。</t>
+          <t>来去原无定处，时来时去安身，跋涉无虞，荣辱不计。</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -19590,7 +19590,7 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>闲云野鹤望东行，惟有乡人便是知音，经营布置两三春，联街灯火后，锦帆前程。</t>
+          <t>闲云野鹤望东行，惟有乡人便是知音，经营布置两三春，联街灯火后，锦片前程。</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -20284,7 +20284,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>耕牛伏軏，辟土开疆，坐看收获，黍稷稻梁。</t>
+          <t>耕牛伏轭，辟土开疆，坐看收获，黍稷稻梁。</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -20732,7 +20732,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>风起西南，红日当天，奇门妙诀，一掌能着。</t>
+          <t>风起西南，红日当天，奇门妙诀，一掌能看。</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -21437,7 +21437,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>山穷路转迷，水急舟难渡，万事莫强为，出处遭研妒。</t>
+          <t>山穷路转迷，水急舟难渡，万事莫强为，出处遭奸妒。</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -21501,7 +21501,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>时边多艰，战战兢兢，戒谨恐惧，如履薄冰，须识前程危与险，一笼风里一枝灯。</t>
+          <t>时变多艰，战战兢兢，戒谨恐惧，如履薄冰，须识前程危与险，一笼风里一枝灯。</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
@@ -23722,7 +23722,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>此去万里程，却遇见知音，同心共济，大立勋名。</t>
+          <t>此去万里程，却遇知音，同心共济，大立勋名。</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
@@ -24155,7 +24155,7 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>世界似清宁，不知辞已休，打叠要小心，须防遭火毐。</t>
+          <t>世界似清宁，不知辞已休，打叠要小心，须防遭火毒。</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
@@ -24599,7 +24599,7 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>疏食饮水，乐在其中，膏梁美味，反使心朦。</t>
+          <t>疏食饮水，乐在其中，膏粱美味，反使心朦。</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
@@ -24729,7 +24729,7 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>蛇可化龙，头角将出，平地一声雷，方显龙蛇力。</t>
+          <t>蛇可化龙，头角将出，平地一声雷轰，方显龙蛇力。</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
@@ -24853,13 +24853,6 @@
           <t>人非孔颜，鲜能无过，过而能改，仍复无过，开花不足凭，结果方为准，放开怀抱意欣欣。</t>
         </is>
       </c>
-      <c r="E385" t="inlineStr"/>
-      <c r="F385" t="inlineStr"/>
-      <c r="G385" t="inlineStr"/>
-      <c r="H385" t="inlineStr"/>
-      <c r="I385" t="inlineStr"/>
-      <c r="J385" t="inlineStr"/>
-      <c r="K385" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
